--- a/history_matching/example/iter0/Cuts/RadiusShouldBe15/test_data.xlsx
+++ b/history_matching/example/iter0/Cuts/RadiusShouldBe15/test_data.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
+  <si>
+    <t>Sample_Id</t>
+  </si>
+  <si>
+    <t>Sim_Id</t>
+  </si>
   <si>
     <t>Sample</t>
   </si>
@@ -61,60 +67,50 @@
     <t>Z_Noiseless</t>
   </si>
   <si>
-    <t>Sample_Id</t>
-  </si>
-  <si>
-    <t>Sim_Id</t>
-  </si>
-  <si>
-    <t>Data_20170414_121534.000018</t>
-  </si>
-  <si>
-    <t>Data_20170414_121534.000019</t>
-  </si>
-  <si>
-    <t>Data_20170414_121534.000020</t>
-  </si>
-  <si>
-    <t>Data_20170414_121534.000021</t>
-  </si>
-  <si>
-    <t>Data_20170414_121534.000022</t>
-  </si>
-  <si>
-    <t>Data_20170414_121534.000023</t>
-  </si>
-  <si>
-    <t>Data_20170414_121534.000024</t>
-  </si>
-  <si>
-    <t>Data_20170414_121534</t>
+    <t>Data_20170712_091645.000018</t>
+  </si>
+  <si>
+    <t>Data_20170712_091645</t>
+  </si>
+  <si>
+    <t>Data_20170712_091645.000019</t>
+  </si>
+  <si>
+    <t>Data_20170712_091645.000020</t>
+  </si>
+  <si>
+    <t>Data_20170712_091645.000021</t>
+  </si>
+  <si>
+    <t>Data_20170712_091645.000022</t>
+  </si>
+  <si>
+    <t>Data_20170712_091645.000023</t>
+  </si>
+  <si>
+    <t>Data_20170712_091645.000024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -129,35 +125,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
 </styleSheet>
 </file>
 
@@ -445,435 +432,439 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>18</v>
       </c>
-      <c r="D2">
-        <v>28.26976625774897</v>
-      </c>
-      <c r="E2">
-        <v>-13.39100428734896</v>
+      <c r="D2" t="n">
+        <v>-16.72196598646099</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.45888310351546</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2">
-        <v>30.38395706671946</v>
-      </c>
-      <c r="H2">
-        <v>39.22237261627167</v>
-      </c>
-      <c r="I2">
-        <v>-8.838415549552209</v>
-      </c>
-      <c r="J2">
-        <v>-11.00559343016802</v>
-      </c>
-      <c r="K2">
-        <v>28.21677918610365</v>
-      </c>
-      <c r="L2">
-        <v>12.81939315272033</v>
-      </c>
-      <c r="M2">
-        <v>11.29361724853516</v>
-      </c>
-      <c r="N2">
-        <v>3.404691390214976</v>
+        <v>18</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46.39499843045764</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.93364303079737</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6.46135539966027</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.746532321510936</v>
+      </c>
+      <c r="K2" t="n">
+        <v>43.6801753523083</v>
+      </c>
+      <c r="L2" t="n">
+        <v>15.5109571986541</v>
+      </c>
+      <c r="M2" t="n">
+        <v>13.14330768585205</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6.805321050395144</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
-      <c r="P2">
-        <v>0.6052862744887448</v>
-      </c>
-      <c r="Q2">
-        <v>0.6448786728022811</v>
+      <c r="P2" t="n">
+        <v>0.6441816486432764</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.6919513300281322</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15.29634713476852</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.04313422864848</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1">
-        <v>19</v>
-      </c>
-      <c r="C3">
-        <v>19</v>
-      </c>
-      <c r="D3">
-        <v>-27.74881279709197</v>
-      </c>
-      <c r="E3">
-        <v>-48.54208872705258</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3">
-        <v>55.82677758100662</v>
-      </c>
-      <c r="H3">
-        <v>37.54372755680007</v>
-      </c>
-      <c r="I3">
-        <v>18.28305002420655</v>
-      </c>
-      <c r="J3">
-        <v>22.93953490655711</v>
-      </c>
-      <c r="K3">
-        <v>60.48326246335718</v>
-      </c>
-      <c r="L3">
-        <v>6.824473984654031</v>
-      </c>
-      <c r="M3">
-        <v>5.298698425292969</v>
-      </c>
-      <c r="N3">
-        <v>15.09874597952494</v>
+      <c r="G3" t="n">
+        <v>84.06699852812513</v>
+      </c>
+      <c r="H3" t="n">
+        <v>78.3866363920115</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.680362136113629</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.636184303673883</v>
+      </c>
+      <c r="K3" t="n">
+        <v>82.02282069568538</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10.51341778521178</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8.145768165588379</v>
+      </c>
+      <c r="N3" t="n">
+        <v>18.76027536954443</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
       </c>
-      <c r="P3">
-        <v>-1.782475651164903</v>
-      </c>
-      <c r="Q3">
-        <v>-2.022896232939491</v>
+      <c r="P3" t="n">
+        <v>0.5721833047733366</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.6340016276377357</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="1">
         <v>20</v>
       </c>
-      <c r="C4">
+      <c r="B4" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D4">
-        <v>-14.90323808547211</v>
-      </c>
-      <c r="E4">
-        <v>73.42646483762144</v>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>37.01032927000048</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14.28531620098244</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4">
-        <v>73.71241013447565</v>
-      </c>
-      <c r="H4">
-        <v>63.31648418182663</v>
-      </c>
-      <c r="I4">
-        <v>10.39592595264902</v>
-      </c>
-      <c r="J4">
-        <v>4.474651849779371</v>
-      </c>
-      <c r="K4">
-        <v>67.791136031606</v>
-      </c>
-      <c r="L4">
-        <v>12.17226509426007</v>
-      </c>
-      <c r="M4">
-        <v>10.64648914337158</v>
-      </c>
-      <c r="N4">
-        <v>13.90094326528972</v>
+        <v>18</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.3699828767349</v>
+      </c>
+      <c r="H4" t="n">
+        <v>38.57586909937373</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7941137773611686</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.161140674112598</v>
+      </c>
+      <c r="K4" t="n">
+        <v>39.73700977348634</v>
+      </c>
+      <c r="L4" t="n">
+        <v>14.36044981990497</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11.99279975891113</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6.069550146243253</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
-      <c r="P4">
-        <v>1.697186093306651</v>
-      </c>
-      <c r="Q4">
-        <v>1.814729744662031</v>
+      <c r="P4" t="n">
+        <v>-0.09005486820159456</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.0972523718046846</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="1">
         <v>21</v>
       </c>
-      <c r="C5">
+      <c r="B5" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="D5">
-        <v>-41.44127180358139</v>
-      </c>
-      <c r="E5">
-        <v>-55.80511911935229</v>
+      <c r="C5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.831376134756006</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-14.57852141958386</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5">
-        <v>70.67363370791277</v>
-      </c>
-      <c r="H5">
-        <v>52.2663603905018</v>
-      </c>
-      <c r="I5">
-        <v>18.40727331741098</v>
-      </c>
-      <c r="J5">
-        <v>21.08980729982651</v>
-      </c>
-      <c r="K5">
-        <v>73.35616769032831</v>
-      </c>
-      <c r="L5">
-        <v>3.352767014039663</v>
-      </c>
-      <c r="M5">
-        <v>1.826991677284241</v>
-      </c>
-      <c r="N5">
-        <v>24.65389159589554</v>
+        <v>18</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15.08660231552476</v>
+      </c>
+      <c r="H5" t="n">
+        <v>24.03868818727185</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-8.952085871747093</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-6.570263022176197</v>
+      </c>
+      <c r="K5" t="n">
+        <v>17.46842516509566</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.624662373242579</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6.257012367248535</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.748534935001841</v>
       </c>
       <c r="O5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>-1.465019970339075</v>
-      </c>
-      <c r="Q5">
-        <v>-1.98461816428503</v>
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.7222733089501464</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.8166216838218315</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="1">
         <v>22</v>
       </c>
-      <c r="C6">
+      <c r="B6" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D6">
-        <v>10.98188747733819</v>
-      </c>
-      <c r="E6">
-        <v>26.91239022115901</v>
+      <c r="C6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D6" t="n">
+        <v>41.12394811855083</v>
+      </c>
+      <c r="E6" t="n">
+        <v>60.41378758903392</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6">
-        <v>28.51923253562785</v>
-      </c>
-      <c r="H6">
-        <v>27.59635549771588</v>
-      </c>
-      <c r="I6">
-        <v>0.9228770379119702</v>
-      </c>
-      <c r="J6">
-        <v>-2.397855397150704</v>
-      </c>
-      <c r="K6">
-        <v>25.19850010056518</v>
-      </c>
-      <c r="L6">
-        <v>4.814031497408538</v>
-      </c>
-      <c r="M6">
-        <v>3.288256168365479</v>
-      </c>
-      <c r="N6">
-        <v>3.837160728278687</v>
+        <v>18</v>
+      </c>
+      <c r="G6" t="n">
+        <v>72.64484137651345</v>
+      </c>
+      <c r="H6" t="n">
+        <v>70.96726632395831</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.677575052555142</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9737328649027349</v>
+      </c>
+      <c r="K6" t="n">
+        <v>71.94099918886104</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.625225634402618</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7.257575988769531</v>
+      </c>
+      <c r="N6" t="n">
+        <v>16.5235800478144</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
       </c>
-      <c r="P6">
-        <v>1.513489528099282</v>
-      </c>
-      <c r="Q6">
-        <v>1.831264419700894</v>
+      <c r="P6" t="n">
+        <v>0.2042463759747042</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2282655580575648</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="1">
         <v>23</v>
       </c>
-      <c r="C7">
+      <c r="B7" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D7">
-        <v>-25.01688191022813</v>
-      </c>
-      <c r="E7">
-        <v>-85.8779545656617</v>
+      <c r="C7" t="n">
+        <v>23</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-44.89685426926108</v>
+      </c>
+      <c r="E7" t="n">
+        <v>72.48911130599336</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7">
-        <v>89.30281350114838</v>
-      </c>
-      <c r="H7">
-        <v>76.39246573406666</v>
-      </c>
-      <c r="I7">
-        <v>12.91034776708172</v>
-      </c>
-      <c r="J7">
-        <v>0.4971231994770243</v>
-      </c>
-      <c r="K7">
-        <v>76.88958893354369</v>
-      </c>
-      <c r="L7">
-        <v>34.3517278136979</v>
-      </c>
-      <c r="M7">
-        <v>32.82595062255859</v>
-      </c>
-      <c r="N7">
-        <v>10.22979202845186</v>
+        <v>18</v>
+      </c>
+      <c r="G7" t="n">
+        <v>86.09220555690713</v>
+      </c>
+      <c r="H7" t="n">
+        <v>83.98573412332803</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.106471433579102</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.016931135366389</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.00266525869442</v>
+      </c>
+      <c r="L7" t="n">
+        <v>29.99904289955459</v>
+      </c>
+      <c r="M7" t="n">
+        <v>27.63139343261719</v>
+      </c>
+      <c r="N7" t="n">
+        <v>12.32696493275797</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
       </c>
-      <c r="P7">
-        <v>2.117923744237125</v>
-      </c>
-      <c r="Q7">
-        <v>2.166586150201071</v>
+      <c r="P7" t="n">
+        <v>0.1918601955977189</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1993163215449146</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="1">
         <v>24</v>
       </c>
-      <c r="C8">
+      <c r="B8" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D8">
-        <v>49.00305676792436</v>
-      </c>
-      <c r="E8">
-        <v>-81.46904140852911</v>
+      <c r="C8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-34.31380334221465</v>
+      </c>
+      <c r="E8" t="n">
+        <v>80.36361379626152</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8">
-        <v>95.11454358416995</v>
-      </c>
-      <c r="H8">
-        <v>367.1484456302171</v>
-      </c>
-      <c r="I8">
-        <v>-272.0339020460472</v>
-      </c>
-      <c r="J8">
-        <v>-7.09167816287195</v>
-      </c>
-      <c r="K8">
-        <v>360.0567674673451</v>
-      </c>
-      <c r="L8">
-        <v>1169.314748052883</v>
-      </c>
-      <c r="M8">
-        <v>1167.788940429688</v>
-      </c>
-      <c r="N8">
-        <v>10.08108790587778</v>
+        <v>18</v>
+      </c>
+      <c r="G8" t="n">
+        <v>87.90710633663716</v>
+      </c>
+      <c r="H8" t="n">
+        <v>84.83780068702788</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.069305649609277</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.05212814297282</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.8899288300007</v>
+      </c>
+      <c r="L8" t="n">
+        <v>25.10801122494924</v>
+      </c>
+      <c r="M8" t="n">
+        <v>22.7403621673584</v>
+      </c>
+      <c r="N8" t="n">
+        <v>13.74440019380249</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
       </c>
-      <c r="P8">
-        <v>-7.747925992972366</v>
-      </c>
-      <c r="Q8">
-        <v>-7.752985784424228</v>
+      <c r="P8" t="n">
+        <v>0.194470838222772</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2034747185520032</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>